--- a/instrumentos/Captura-Linea-Base-Alma-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Alma-2026.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Los números del centro · Centro de Excelencia Implantológica Alma</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v27.0 · Ejercicio 2026</t>
+    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v28.0 · Ejercicio 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Para qué sirve</t>

--- a/instrumentos/Captura-Linea-Base-Alma-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Alma-2026.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Los números del centro · Centro de Excelencia Implantológica Alma</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v28.0 · Ejercicio 2026</t>
+    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v29.0 · Ejercicio 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Para qué sirve</t>

--- a/instrumentos/Captura-Linea-Base-Alma-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Alma-2026.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Los números del centro · Centro de Excelencia Implantológica Alma</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v29.0 · Ejercicio 2026</t>
+    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v30.0 · Ejercicio 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Para qué sirve</t>

--- a/instrumentos/Captura-Linea-Base-Alma-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Alma-2026.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Los números del centro · Centro de Excelencia Implantológica Alma</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v30.0 · Ejercicio 2026</t>
+    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v31.0 · Ejercicio 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Para qué sirve</t>

--- a/instrumentos/Captura-Linea-Base-Alma-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Alma-2026.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Los números del centro · Centro de Excelencia Implantológica Alma</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v31.0 · Ejercicio 2026</t>
+    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v32.0 · Ejercicio 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Para qué sirve</t>
